--- a/Submit/Results/hoangbsthe186345/TC3_ReqResNotC/TC3_ReqResNotC_Result.xlsx
+++ b/Submit/Results/hoangbsthe186345/TC3_ReqResNotC/TC3_ReqResNotC_Result.xlsx
@@ -31,7 +31,7 @@
     <x:t>TC3_ReqResNotC</x:t>
   </x:si>
   <x:si>
-    <x:t>FAIL</x:t>
+    <x:t>PASS</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -428,7 +428,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="C2" s="0">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="D2" s="0">
         <x:v>1</x:v>
